--- a/exports/BHEL_full_report.xlsx
+++ b/exports/BHEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>61.9</v>
+        <v>60.1</v>
       </c>
       <c r="I2" t="n">
         <v>60.25757598602875</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8</v>
+        <v>-3.69</v>
       </c>
       <c r="L2" t="n">
-        <v>4.33</v>
+        <v>5.93</v>
       </c>
       <c r="M2" t="n">
         <v>0.8100000000000001</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>49.95</v>
+        <v>50.3</v>
       </c>
       <c r="I3" t="n">
         <v>50.13395017593485</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>38</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>16.89</v>
+        <v>16.31</v>
       </c>
       <c r="L3" t="n">
         <v>3.16</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44648.55208333334</v>
+        <v>44649.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>49.85</v>
+        <v>48.9</v>
       </c>
       <c r="I4" t="n">
         <v>48.96920877111065</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.89</v>
+        <v>-2.78</v>
       </c>
       <c r="L4" t="n">
         <v>5.57</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.06</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>49.3</v>
+        <v>53.2</v>
       </c>
       <c r="I5" t="n">
         <v>52.18185874792822</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.82</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>3.78</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>-1.4</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>54.8</v>
+        <v>52.85</v>
       </c>
       <c r="I6" t="n">
         <v>53.63931951934239</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>3.01</v>
+        <v>-0.66</v>
       </c>
       <c r="L6" t="n">
         <v>6.95</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>49.5</v>
+        <v>51.9</v>
       </c>
       <c r="I7" t="n">
         <v>50.47843509405338</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>6.34</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
         <v>5.68</v>
@@ -840,7 +923,7 @@
         <v>1.98</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>7.98</v>
       </c>
       <c r="O7" t="n">
         <v>-2.94</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>10.73</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>49.85</v>
+        <v>47.85</v>
       </c>
       <c r="I8" t="n">
         <v>48.90928450266234</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.95</v>
+        <v>-7.8</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="N8" t="n">
         <v>4.58</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.67</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>45.5</v>
+        <v>46.4</v>
       </c>
       <c r="I9" t="n">
         <v>45.77092530545399</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>4.91</v>
+        <v>3.03</v>
       </c>
       <c r="L9" t="n">
         <v>2.82</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.78</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44778.38541666666</v>
+        <v>44778.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>51.9</v>
+        <v>51.55</v>
       </c>
       <c r="I10" t="n">
         <v>51.61631618327544</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>11.85</v>
+        <v>11.1</v>
       </c>
       <c r="L10" t="n">
         <v>4.31</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.13</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44790.55208333334</v>
+        <v>44791.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>53.65</v>
+        <v>56.1</v>
       </c>
       <c r="I11" t="n">
         <v>54.96227611097182</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.07</v>
+        <v>-8.83</v>
       </c>
       <c r="L11" t="n">
-        <v>5.24</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0.76</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>4.85</v>
       </c>
       <c r="O11" t="n">
         <v>-2.27</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.79</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>54</v>
+        <v>52.8</v>
       </c>
       <c r="I12" t="n">
         <v>52.81262413744412</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.74</v>
+        <v>-5.88</v>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>6.33</v>
       </c>
       <c r="M12" t="n">
         <v>0.09</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.92</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>53.25</v>
+        <v>58.1</v>
       </c>
       <c r="I13" t="n">
         <v>56.02341230342292</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.85</v>
+        <v>-10.04</v>
       </c>
       <c r="L13" t="n">
-        <v>2.46</v>
+        <v>11.93</v>
       </c>
       <c r="M13" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="N13" t="n">
-        <v>1.05</v>
+        <v>7.7</v>
       </c>
       <c r="O13" t="n">
         <v>-3.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>61.45</v>
+        <v>59.55</v>
       </c>
       <c r="I14" t="n">
         <v>60.09437454058159</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>5.77</v>
+        <v>2.5</v>
       </c>
       <c r="L14" t="n">
         <v>7.92</v>
@@ -1239,7 +1406,7 @@
         <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.54</v>
+        <v>3.17</v>
       </c>
       <c r="O14" t="n">
         <v>7.7</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44834.38541666666</v>
+        <v>44834.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>59.65</v>
+        <v>59.9</v>
       </c>
       <c r="I15" t="n">
         <v>59.6590532753095</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.17</v>
+        <v>-0.59</v>
       </c>
       <c r="L15" t="n">
         <v>4.2</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.48</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>74.25</v>
+        <v>69.25</v>
       </c>
       <c r="I16" t="n">
         <v>71.784199175705</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>42</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>23.96</v>
+        <v>15.61</v>
       </c>
       <c r="L16" t="n">
         <v>0.67</v>
       </c>
       <c r="M16" t="n">
-        <v>1.49</v>
+        <v>6.67</v>
       </c>
       <c r="N16" t="n">
-        <v>4.26</v>
+        <v>4.51</v>
       </c>
       <c r="O16" t="n">
         <v>2.04</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>10.38</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44887.55208333334</v>
+        <v>44888.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>74.25</v>
+        <v>75.45</v>
       </c>
       <c r="I17" t="n">
         <v>75.00876657073616</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.22</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>8.66</v>
+        <v>10.04</v>
       </c>
       <c r="M17" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="N17" t="n">
         <v>3.27</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>84</v>
+        <v>82.2</v>
       </c>
       <c r="I18" t="n">
         <v>83.47582943603359</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>11.33</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>1.72</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>69.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I19" t="n">
         <v>71.1731116912044</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K19" t="n">
-        <v>15.33</v>
+        <v>12.17</v>
       </c>
       <c r="L19" t="n">
         <v>5.9</v>
@@ -1524,7 +1751,7 @@
         <v>6.67</v>
       </c>
       <c r="N19" t="n">
-        <v>3.92</v>
+        <v>4.67</v>
       </c>
       <c r="O19" t="n">
         <v>-3.45</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.58</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45008.55208333334</v>
+        <v>45009.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>74.15000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="I20" t="n">
         <v>73.99692943922273</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>1.45</v>
       </c>
       <c r="L20" t="n">
         <v>3.6</v>
@@ -1581,7 +1820,7 @@
         <v>1.94</v>
       </c>
       <c r="N20" t="n">
-        <v>3.19</v>
+        <v>3.44</v>
       </c>
       <c r="O20" t="n">
         <v>4.67</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.87</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45027.38541666666</v>
+        <v>45027.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="I21" t="n">
         <v>71.97300456159041</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>2.39</v>
+        <v>1.71</v>
       </c>
       <c r="L21" t="n">
         <v>1.71</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>85.95</v>
+        <v>81.25</v>
       </c>
       <c r="I22" t="n">
         <v>81.72474186691139</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>19.38</v>
+        <v>12.85</v>
       </c>
       <c r="L22" t="n">
         <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="N22" t="n">
-        <v>1.31</v>
+        <v>5.93</v>
       </c>
       <c r="O22" t="n">
         <v>0.98</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.25</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45079.55208333334</v>
+        <v>45082.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>83.05</v>
+        <v>85.05</v>
       </c>
       <c r="I23" t="n">
         <v>83.78169545607324</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.22</v>
+        <v>-4.68</v>
       </c>
       <c r="L23" t="n">
         <v>5.29</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.73</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45100.55208333334</v>
+        <v>45103.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>84.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>83.89469985145014</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.41</v>
+        <v>-1.7</v>
       </c>
       <c r="L24" t="n">
         <v>3.35</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.37</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45110.38541666666</v>
+        <v>45110.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>88.09999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="I25" t="n">
         <v>88.1978643810168</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.38</v>
+        <v>-5.8</v>
       </c>
       <c r="L25" t="n">
         <v>6.64</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>100.4</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>99.79934250294434</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>13.51</v>
+        <v>12.61</v>
       </c>
       <c r="L26" t="n">
         <v>2.04</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.87</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45160.38541666666</v>
+        <v>45160.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>103.7</v>
+        <v>110.8</v>
       </c>
       <c r="I27" t="n">
         <v>103.8611795033808</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.12</v>
+        <v>-11.24</v>
       </c>
       <c r="L27" t="n">
-        <v>4.37</v>
+        <v>13.3</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>140</v>
+        <v>129.25</v>
       </c>
       <c r="I28" t="n">
         <v>132.2372729980856</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>26.35</v>
+        <v>16.65</v>
       </c>
       <c r="L28" t="n">
         <v>6.45</v>
@@ -2037,7 +2372,7 @@
         <v>0.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.38</v>
+        <v>10.21</v>
       </c>
       <c r="O28" t="n">
         <v>9.869999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>16.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>125.95</v>
+        <v>128.1</v>
       </c>
       <c r="I29" t="n">
         <v>126.0701867591511</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>2.55</v>
+        <v>0.89</v>
       </c>
       <c r="L29" t="n">
         <v>9.48</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>184.5</v>
+        <v>171.25</v>
       </c>
       <c r="I30" t="n">
         <v>174.109744609653</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>44.03</v>
+        <v>33.68</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.05</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45288.38541666666</v>
+        <v>45288.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>190.35</v>
+        <v>192</v>
       </c>
       <c r="I31" t="n">
         <v>191.6816068661811</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.15</v>
+        <v>-12.12</v>
       </c>
       <c r="L31" t="n">
-        <v>12.12</v>
+        <v>13.26</v>
       </c>
       <c r="M31" t="n">
         <v>0.86</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>219.35</v>
+        <v>216.5</v>
       </c>
       <c r="I32" t="n">
         <v>217.187788912125</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K32" t="n">
-        <v>14.24</v>
+        <v>12.76</v>
       </c>
       <c r="L32" t="n">
         <v>1.02</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>12.23</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>232.9</v>
+        <v>265.75</v>
       </c>
       <c r="I33" t="n">
         <v>235.5916210503969</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.58</v>
+        <v>-22.75</v>
       </c>
       <c r="L33" t="n">
-        <v>9.630000000000001</v>
+        <v>24.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="N33" t="n">
-        <v>5.13</v>
+        <v>13.85</v>
       </c>
       <c r="O33" t="n">
         <v>-5.04</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>15.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>244</v>
+        <v>231.3</v>
       </c>
       <c r="I34" t="n">
         <v>239.9317236144598</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.18</v>
+        <v>-12.96</v>
       </c>
       <c r="L34" t="n">
-        <v>10.78</v>
+        <v>14.45</v>
       </c>
       <c r="M34" t="n">
         <v>0.04</v>
       </c>
       <c r="N34" t="n">
-        <v>5.03</v>
+        <v>7.87</v>
       </c>
       <c r="O34" t="n">
         <v>13.85</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.13</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>239.75</v>
+        <v>244.8</v>
       </c>
       <c r="I35" t="n">
         <v>244.7380530163603</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.65</v>
+        <v>-5.84</v>
       </c>
       <c r="L35" t="n">
-        <v>6.46</v>
+        <v>7.87</v>
       </c>
       <c r="M35" t="n">
         <v>2.29</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.43</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>288.8</v>
+        <v>277.1</v>
       </c>
       <c r="I36" t="n">
         <v>280.8288669626147</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>17.97</v>
+        <v>13.19</v>
       </c>
       <c r="L36" t="n">
         <v>1.76</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>13.62</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45429.38541666666</v>
+        <v>45429.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>295</v>
+        <v>301.5</v>
       </c>
       <c r="I37" t="n">
         <v>300.7423188541051</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.46</v>
+        <v>-8.81</v>
       </c>
       <c r="L37" t="n">
-        <v>7.4</v>
+        <v>8.91</v>
       </c>
       <c r="M37" t="n">
         <v>0.8100000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>299.1</v>
+        <v>293.5</v>
       </c>
       <c r="I38" t="n">
         <v>294.8625865171182</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.8</v>
+        <v>-2.65</v>
       </c>
       <c r="L38" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="M38" t="n">
         <v>5.21</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>295.3</v>
+        <v>296.55</v>
       </c>
       <c r="I39" t="n">
         <v>296.3890521507064</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.61</v>
+        <v>-1.04</v>
       </c>
       <c r="L39" t="n">
         <v>9.369999999999999</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45491.38541666666</v>
+        <v>45491.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>311.15</v>
+        <v>308</v>
       </c>
       <c r="I40" t="n">
         <v>310.8139000920587</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>4.92</v>
+        <v>3.86</v>
       </c>
       <c r="L40" t="n">
         <v>2.71</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>7.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>316.6</v>
+        <v>319.85</v>
       </c>
       <c r="I41" t="n">
         <v>319.4299841782862</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.79</v>
+        <v>-3.85</v>
       </c>
       <c r="L41" t="n">
-        <v>3.33</v>
+        <v>6.17</v>
       </c>
       <c r="M41" t="n">
-        <v>0.55</v>
+        <v>3.28</v>
       </c>
       <c r="N41" t="n">
         <v>3.72</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.81</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.38541666666</v>
+        <v>45506.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>303.95</v>
+        <v>300.85</v>
       </c>
       <c r="I42" t="n">
         <v>300.8964483428225</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.97</v>
+        <v>-5.94</v>
       </c>
       <c r="L42" t="n">
-        <v>5.82</v>
+        <v>6.02</v>
       </c>
       <c r="M42" t="n">
         <v>1.69</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>8.01</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>266.2</v>
+        <v>273.45</v>
       </c>
       <c r="I43" t="n">
         <v>272.439993372687</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>11.52</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L43" t="n">
         <v>1.65</v>
       </c>
       <c r="M43" t="n">
-        <v>1.96</v>
+        <v>2.93</v>
       </c>
       <c r="N43" t="n">
         <v>6.2</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.32</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>279.9</v>
+        <v>268.95</v>
       </c>
       <c r="I44" t="n">
         <v>270.9275442174285</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>2.36</v>
+        <v>-1.65</v>
       </c>
       <c r="L44" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="M44" t="n">
-        <v>-0</v>
+        <v>2.04</v>
       </c>
       <c r="N44" t="n">
-        <v>1.67</v>
+        <v>3.97</v>
       </c>
       <c r="O44" t="n">
         <v>2.95</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>235</v>
+        <v>241.65</v>
       </c>
       <c r="I45" t="n">
         <v>239.3257939291679</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>12.62</v>
+        <v>10.15</v>
       </c>
       <c r="L45" t="n">
         <v>3.31</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>12.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>229.5</v>
+        <v>225.01</v>
       </c>
       <c r="I46" t="n">
         <v>227.278994498416</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.03</v>
+        <v>-6.89</v>
       </c>
       <c r="L46" t="n">
-        <v>5.23</v>
+        <v>7.92</v>
       </c>
       <c r="M46" t="n">
         <v>0.25</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.67</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>235</v>
+        <v>244.61</v>
       </c>
       <c r="I47" t="n">
         <v>240.4870796940697</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.44</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>4.95</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>0.75</v>
+        <v>2.94</v>
       </c>
       <c r="N47" t="n">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="O47" t="n">
         <v>-3.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.5</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>242.25</v>
+        <v>241.15</v>
       </c>
       <c r="I48" t="n">
         <v>241.8023612026522</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="L48" t="n">
         <v>2.97</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.38</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45674.38541666666</v>
+        <v>45674.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>212.39</v>
+        <v>213.9</v>
       </c>
       <c r="I49" t="n">
         <v>212.4159050049134</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>11.93</v>
+        <v>11.3</v>
       </c>
       <c r="L49" t="n">
         <v>1.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.8</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>209.2</v>
+        <v>201.7</v>
       </c>
       <c r="I50" t="n">
         <v>202.343039977809</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.2</v>
+        <v>-5.7</v>
       </c>
       <c r="L50" t="n">
-        <v>2.38</v>
+        <v>6.12</v>
       </c>
       <c r="M50" t="n">
         <v>0.07000000000000001</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>206.85</v>
+        <v>208.4</v>
       </c>
       <c r="I51" t="n">
         <v>207.6054201263643</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.55</v>
+        <v>-3.32</v>
       </c>
       <c r="L51" t="n">
         <v>4.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>9.67</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45705.55208333334</v>
+        <v>45706.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>193.55</v>
+        <v>184.75</v>
       </c>
       <c r="I52" t="n">
         <v>189.3532176024602</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.13</v>
+        <v>-11.35</v>
       </c>
       <c r="L52" t="n">
-        <v>9.550000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="M52" t="n">
         <v>0.84</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>13.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>191.91</v>
+        <v>196.25</v>
       </c>
       <c r="I53" t="n">
         <v>195.9230089443298</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.88</v>
+        <v>-6.22</v>
       </c>
       <c r="L53" t="n">
         <v>9.42</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>9.66</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>214.4</v>
+        <v>203.45</v>
       </c>
       <c r="I54" t="n">
         <v>205.0359908066707</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K54" t="n">
-        <v>9.25</v>
+        <v>3.67</v>
       </c>
       <c r="L54" t="n">
         <v>4.2</v>
       </c>
       <c r="M54" t="n">
-        <v>1.44</v>
+        <v>9.51</v>
       </c>
       <c r="N54" t="n">
         <v>2.65</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.35</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>220.3</v>
+        <v>222.13</v>
       </c>
       <c r="I55" t="n">
         <v>220.4427471871335</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.279999999999999</v>
+        <v>-9.18</v>
       </c>
       <c r="L55" t="n">
-        <v>8.630000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="M55" t="n">
         <v>2.05</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>216.48</v>
+        <v>214.97</v>
       </c>
       <c r="I56" t="n">
         <v>216.3344548009737</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.54</v>
+        <v>-3.22</v>
       </c>
       <c r="L56" t="n">
-        <v>3.93</v>
+        <v>4.52</v>
       </c>
       <c r="M56" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="N56" t="n">
         <v>5.42</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.82</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>230.92</v>
+        <v>233.49</v>
       </c>
       <c r="I57" t="n">
         <v>231.7751596239284</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.42</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>8.42</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M57" t="n">
         <v>3.15</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45811.55208333334</v>
+        <v>45812.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>252.9</v>
+        <v>251.75</v>
       </c>
       <c r="I58" t="n">
         <v>252.1319218511488</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>8.31</v>
+        <v>7.82</v>
       </c>
       <c r="L58" t="n">
         <v>1.19</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.24</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>253.4</v>
+        <v>263.25</v>
       </c>
       <c r="I59" t="n">
         <v>259.9078081071987</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.66</v>
+        <v>-4.57</v>
       </c>
       <c r="L59" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="M59" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.57</v>
+        <v>2.74</v>
       </c>
       <c r="O59" t="n">
         <v>0.36</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.63</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>254.15</v>
+        <v>253.7</v>
       </c>
       <c r="I60" t="n">
         <v>253.7557963184822</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.46</v>
+        <v>-3.63</v>
       </c>
       <c r="L60" t="n">
-        <v>3.78</v>
+        <v>4.22</v>
       </c>
       <c r="M60" t="n">
         <v>0.41</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>4.23</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>241.75</v>
+        <v>246.09</v>
       </c>
       <c r="I61" t="n">
         <v>243.8847413114972</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>4.71</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
         <v>1.06</v>
       </c>
       <c r="M61" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="N61" t="n">
         <v>4.18</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.68</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45875.55208333334</v>
+        <v>45876.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>239.25</v>
+        <v>223.62</v>
       </c>
       <c r="I62" t="n">
         <v>234.0860972255267</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.78</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>3.12</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>0.02</v>
+        <v>3.09</v>
       </c>
       <c r="N62" t="n">
-        <v>3.72</v>
+        <v>4.63</v>
       </c>
       <c r="O62" t="n">
         <v>2.79</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.82</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>214.95</v>
+        <v>220</v>
       </c>
       <c r="I63" t="n">
         <v>218.5330447779789</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>3.88</v>
+        <v>1.62</v>
       </c>
       <c r="L63" t="n">
         <v>4.06</v>
@@ -4032,7 +4787,7 @@
         <v>2.04</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>-4.63</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.14</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45943.38541666666</v>
+        <v>45943.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>235.38</v>
+        <v>234.3</v>
       </c>
       <c r="I64" t="n">
         <v>235.1145895397746</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>6.99</v>
+        <v>6.5</v>
       </c>
       <c r="L64" t="n">
         <v>2.7</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.07</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>237</v>
+        <v>244.51</v>
       </c>
       <c r="I65" t="n">
         <v>242.3206819830824</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.15</v>
+        <v>-4.36</v>
       </c>
       <c r="L65" t="n">
-        <v>1.85</v>
+        <v>4.48</v>
       </c>
       <c r="M65" t="n">
         <v>0.61</v>
       </c>
       <c r="N65" t="n">
-        <v>1.75</v>
+        <v>3.85</v>
       </c>
       <c r="O65" t="n">
         <v>-2.37</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.3</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>286.55</v>
+        <v>279.8</v>
       </c>
       <c r="I66" t="n">
         <v>280.0576275534324</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K66" t="n">
-        <v>17.19</v>
+        <v>14.43</v>
       </c>
       <c r="L66" t="n">
         <v>3.07</v>
@@ -4203,7 +4994,7 @@
         <v>1.02</v>
       </c>
       <c r="N66" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="O66" t="n">
         <v>3.85</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46002.55208333334</v>
+        <v>46003.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>276.4</v>
+        <v>285.15</v>
       </c>
       <c r="I67" t="n">
         <v>283.3255885960844</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K67" t="n">
-        <v>1.22</v>
+        <v>-1.91</v>
       </c>
       <c r="L67" t="n">
         <v>2.82</v>
@@ -4260,7 +5063,7 @@
         <v>0.18</v>
       </c>
       <c r="N67" t="n">
-        <v>2.57</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>-2.76</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.9</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>295.05</v>
+        <v>276.8</v>
       </c>
       <c r="I68" t="n">
         <v>288.1207520710205</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>3.47</v>
+        <v>-2.93</v>
       </c>
       <c r="L68" t="n">
-        <v>4.8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M68" t="n">
         <v>0.32</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>258.4</v>
+        <v>267.1</v>
       </c>
       <c r="I69" t="n">
         <v>264.7588442240959</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>6.65</v>
+        <v>3.5</v>
       </c>
       <c r="L69" t="n">
         <v>6.7</v>
       </c>
       <c r="M69" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
         <v>4.94</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.84</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46066.38541666666</v>
+        <v>46066.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>260.5</v>
+        <v>255.3</v>
       </c>
       <c r="I70" t="n">
         <v>257.2903448723278</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.47</v>
+        <v>-4.42</v>
       </c>
       <c r="L70" t="n">
         <v>4.64</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>255.8</v>
+        <v>268.15</v>
       </c>
       <c r="I71" t="n">
         <v>267.2880022347489</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.2</v>
+        <v>-5.03</v>
       </c>
       <c r="L71" t="n">
-        <v>4.94</v>
+        <v>5.9</v>
       </c>
       <c r="M71" t="n">
         <v>1.35</v>
       </c>
       <c r="N71" t="n">
-        <v>3.65</v>
+        <v>4.42</v>
       </c>
       <c r="O71" t="n">
         <v>-1.75</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>11.04</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46111.38541666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="I72" t="n">
         <v>247.2328751987913</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.65</v>
+        <v>-8.26</v>
       </c>
       <c r="L72" t="n">
-        <v>7.27</v>
+        <v>9.01</v>
       </c>
       <c r="M72" t="n">
         <v>1.82</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>265.96</v>
+        <v>277.92</v>
       </c>
       <c r="I73" t="n">
         <v>266.5501218105947</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.109999999999999</v>
+        <v>-12.98</v>
       </c>
       <c r="L73" t="n">
-        <v>8.859999999999999</v>
+        <v>14.23</v>
       </c>
       <c r="M73" t="n">
         <v>3.46</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.72</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46177.38541666666</v>
+        <v>46177.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>402.75</v>
+        <v>387.4</v>
       </c>
       <c r="I74" t="n">
         <v>400.4302079176219</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K74" t="n">
-        <v>44.92</v>
+        <v>39.39</v>
       </c>
       <c r="L74" t="n">
         <v>5.09</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>392.15</v>
+        <v>405.75</v>
       </c>
       <c r="I75" t="n">
         <v>400.433816095619</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.23</v>
+        <v>-4.74</v>
       </c>
       <c r="L75" t="n">
-        <v>4.18</v>
+        <v>4.97</v>
       </c>
       <c r="M75" t="n">
         <v>2.28</v>
       </c>
       <c r="N75" t="n">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="O75" t="n">
         <v>-4.36</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>8.31</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>402</v>
+        <v>385.85</v>
       </c>
       <c r="I76" t="n">
         <v>389.7956027305551</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.92</v>
+        <v>-4.9</v>
       </c>
       <c r="L76" t="n">
-        <v>3.55</v>
+        <v>5.29</v>
       </c>
       <c r="M76" t="n">
         <v>0.43</v>
       </c>
       <c r="N76" t="n">
-        <v>2.97</v>
+        <v>4.65</v>
       </c>
       <c r="O76" t="n">
         <v>3.28</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>395</v>
+        <v>409.65</v>
       </c>
       <c r="I77" t="n">
         <v>403.3549682984786</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.37</v>
+        <v>-6.17</v>
       </c>
       <c r="L77" t="n">
-        <v>4.5</v>
+        <v>6.78</v>
       </c>
       <c r="M77" t="n">
         <v>1.7</v>
       </c>
       <c r="N77" t="n">
-        <v>3.29</v>
+        <v>3.49</v>
       </c>
       <c r="O77" t="n">
         <v>-4.65</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>9.77</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>414.15</v>
+        <v>411</v>
       </c>
       <c r="I78" t="n">
         <v>411.387538329109</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K78" t="n">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="L78" t="n">
         <v>4.89</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>5.81</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>416.7</v>
+        <v>431.45</v>
       </c>
       <c r="I79" t="n">
         <v>428.729854297035</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.39</v>
+        <v>-4.98</v>
       </c>
       <c r="L79" t="n">
-        <v>2.43</v>
+        <v>6.62</v>
       </c>
       <c r="M79" t="n">
         <v>0.71</v>
       </c>
       <c r="N79" t="n">
-        <v>1.5</v>
+        <v>3.96</v>
       </c>
       <c r="O79" t="n">
         <v>-1.1</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.08</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46280.55208333334</v>
+        <v>46281.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>415.05</v>
+        <v>412.5</v>
       </c>
       <c r="I80" t="n">
         <v>413.4770146161692</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.8</v>
+        <v>-4.39</v>
       </c>
       <c r="L80" t="n">
-        <v>4.14</v>
+        <v>5.9</v>
       </c>
       <c r="M80" t="n">
         <v>0.4</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>5.69</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>427.9</v>
+        <v>450.55</v>
       </c>
       <c r="I81" t="n">
         <v>434.3311568783429</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.73</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>6.59</v>
+        <v>9.33</v>
       </c>
       <c r="M81" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>3.77</v>
+        <v>5.52</v>
       </c>
       <c r="O81" t="n">
         <v>-0.67</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>9.34</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>426.9</v>
+        <v>411.65</v>
       </c>
       <c r="I82" t="n">
         <v>422.6230885184964</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K82" t="n">
-        <v>-5.25</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>6.64</v>
+        <v>8.73</v>
       </c>
       <c r="M82" t="n">
         <v>2.49</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,12 @@
       <c r="Q83" t="n">
         <v>10</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7277,7 +8278,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="6">
@@ -7287,7 +8288,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -7297,7 +8298,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -7307,7 +8308,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7317,7 +8318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10">
@@ -7327,7 +8328,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="11">
@@ -7337,7 +8338,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -7347,7 +8348,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -7357,7 +8358,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80.2</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="14">
@@ -7367,7 +8368,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.78</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="15">
@@ -7377,7 +8378,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.53</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="16">
@@ -7387,7 +8388,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="17">
@@ -7397,7 +8398,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.92</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="18">
@@ -7407,7 +8408,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -7417,7 +8418,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.78</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="20">
@@ -7427,7 +8428,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.33</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="21">
@@ -7437,7 +8438,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.12</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="22">
@@ -7447,7 +8448,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -7457,7 +8458,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -7467,7 +8468,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="25">
@@ -7477,7 +8478,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.21</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="26">
@@ -7487,7 +8488,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.15</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="27">
@@ -7497,7 +8498,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.869999999999999</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="28">
@@ -7507,7 +8508,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
